--- a/ملف مجمع لتدبر القرآن.xlsx
+++ b/ملف مجمع لتدبر القرآن.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\سور القرآن\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Quran_Analysis_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B8EDEB-52AE-44C4-A2FC-209508364ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
     <definedName name="Slicer_كود_المجموعة">#N/A</definedName>
     <definedName name="Slicer_كود_النصف">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -1495,7 +1496,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1983,20 +1984,26 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>376</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>923925</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>371475</xdr:rowOff>
+      <xdr:row>388</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="كود النصف"/>
+            <xdr:cNvPr id="2" name="كود النصف">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -2055,20 +2062,26 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>615315</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="كود الربع "/>
+            <xdr:cNvPr id="3" name="كود الربع ">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -2082,7 +2095,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2127,20 +2140,26 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>605790</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="كود المجموعة"/>
+            <xdr:cNvPr id="4" name="كود المجموعة">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -2154,7 +2173,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2199,20 +2218,26 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>615315</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>2009775</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>685800</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>320040</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="بيان التقسيم لأرباع القرآن"/>
+            <xdr:cNvPr id="5" name="بيان التقسيم لأرباع القرآن">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -2226,7 +2251,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2271,7 +2296,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_كود_النصف" sourceName="كود النصف">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_كود_النصف" xr10:uid="{00000000-0013-0000-FFFF-FFFF01000000}" sourceName="كود النصف">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="5"/>
@@ -2281,7 +2306,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_كود_الربع" sourceName="كود الربع ">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_كود_الربع" xr10:uid="{00000000-0013-0000-FFFF-FFFF02000000}" sourceName="كود الربع ">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="6"/>
@@ -2291,7 +2316,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_كود_المجموعة" sourceName="كود المجموعة">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_كود_المجموعة" xr10:uid="{00000000-0013-0000-FFFF-FFFF03000000}" sourceName="كود المجموعة">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="8"/>
@@ -2301,7 +2326,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_بيان_التقسيم_لأرباع_القرآن" sourceName="بيان التقسيم لأرباع القرآن">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_بيان_التقسيم_لأرباع_القرآن" xr10:uid="{00000000-0013-0000-FFFF-FFFF04000000}" sourceName="بيان التقسيم لأرباع القرآن">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="9"/>
@@ -2311,39 +2336,45 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <slicer name="كود النصف" cache="Slicer_كود_النصف" caption="كود النصف" rowHeight="241300"/>
-  <slicer name="كود الربع " cache="Slicer_كود_الربع" caption="كود الربع " rowHeight="241300"/>
-  <slicer name="كود المجموعة" cache="Slicer_كود_المجموعة" caption="كود المجموعة" rowHeight="241300"/>
-  <slicer name="بيان التقسيم لأرباع القرآن" cache="Slicer_بيان_التقسيم_لأرباع_القرآن" caption="بيان التقسيم لأرباع القرآن" rowHeight="241300"/>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="كود النصف" xr10:uid="{00000000-0014-0000-FFFF-FFFF01000000}" cache="Slicer_كود_النصف" caption="كود النصف" rowHeight="241300"/>
+  <slicer name="كود الربع " xr10:uid="{00000000-0014-0000-FFFF-FFFF02000000}" cache="Slicer_كود_الربع" caption="كود الربع " rowHeight="241300"/>
+  <slicer name="كود المجموعة" xr10:uid="{00000000-0014-0000-FFFF-FFFF03000000}" cache="Slicer_كود_المجموعة" caption="كود المجموعة" rowHeight="241300"/>
+  <slicer name="بيان التقسيم لأرباع القرآن" xr10:uid="{00000000-0014-0000-FFFF-FFFF04000000}" cache="Slicer_بيان_التقسيم_لأرباع_القرآن" caption="بيان التقسيم لأرباع القرآن" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L115" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:L115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:L115" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:L115" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="1.2.4.7"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="1" name="م" dataDxfId="11"/>
-    <tableColumn id="2" name="إسم السورة" dataDxfId="10"/>
-    <tableColumn id="3" name="عدد الآيات" dataDxfId="9"/>
-    <tableColumn id="4" name="بداية السورة" dataDxfId="8"/>
-    <tableColumn id="5" name="كود النصف" dataDxfId="7"/>
-    <tableColumn id="6" name="كود الربع " dataDxfId="6"/>
-    <tableColumn id="7" name="بيان الدعوة لنصفى القرآن" dataDxfId="5"/>
-    <tableColumn id="8" name="كود المجموعة" dataDxfId="4"/>
-    <tableColumn id="9" name="بيان التقسيم لأرباع القرآن" dataDxfId="3"/>
-    <tableColumn id="10" name="كود السورة" dataDxfId="2"/>
-    <tableColumn id="11" name="بيان مقاصد السور" dataDxfId="1"/>
-    <tableColumn id="12" name="تفاصيل مقاصد المجموعات الثمانى من السور" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="م" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="إسم السورة" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="عدد الآيات" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="بداية السورة" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="كود النصف" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="كود الربع " dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="بيان الدعوة لنصفى القرآن" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="كود المجموعة" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="بيان التقسيم لأرباع القرآن" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="كود السورة" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="بيان مقاصد السور" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="تفاصيل مقاصد المجموعات الثمانى من السور" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2381,9 +2412,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2418,7 +2449,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2453,7 +2484,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2626,24 +2657,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L115"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="75.85546875" customWidth="1"/>
-    <col min="12" max="12" width="79.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="75.88671875" customWidth="1"/>
+    <col min="12" max="12" width="79.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2681,7 +2712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2719,7 +2750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2757,7 +2788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2795,7 +2826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2833,7 +2864,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2871,7 +2902,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2909,7 +2940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2947,7 +2978,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2985,7 +3016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3023,7 +3054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3061,7 +3092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3099,7 +3130,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3137,7 +3168,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3175,7 +3206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3213,7 +3244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3251,7 +3282,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3289,7 +3320,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3327,7 +3358,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3365,7 +3396,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3403,7 +3434,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3441,7 +3472,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3479,7 +3510,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3517,7 +3548,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3555,7 +3586,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3593,7 +3624,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3631,7 +3662,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3669,7 +3700,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3707,7 +3738,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3745,7 +3776,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3783,7 +3814,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3821,7 +3852,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3859,7 +3890,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3897,7 +3928,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3935,7 +3966,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3973,7 +4004,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -4011,7 +4042,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -4049,7 +4080,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4087,7 +4118,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4125,7 +4156,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4163,7 +4194,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4201,7 +4232,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4239,7 +4270,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4277,7 +4308,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4315,7 +4346,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4353,7 +4384,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4391,7 +4422,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4429,7 +4460,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4467,7 +4498,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4505,7 +4536,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4543,7 +4574,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4581,7 +4612,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -4619,7 +4650,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4657,7 +4688,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4695,7 +4726,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4733,7 +4764,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4771,7 +4802,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4809,7 +4840,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4847,7 +4878,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4885,7 +4916,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4923,7 +4954,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4961,7 +4992,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4999,7 +5030,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5037,7 +5068,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5075,7 +5106,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -5113,7 +5144,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -5151,7 +5182,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -5189,7 +5220,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -5227,7 +5258,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5265,7 +5296,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5303,7 +5334,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5341,7 +5372,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -5379,7 +5410,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5417,7 +5448,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -5455,7 +5486,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -5493,7 +5524,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -5531,7 +5562,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -5569,7 +5600,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -5607,7 +5638,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -5645,7 +5676,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -5683,7 +5714,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -5721,7 +5752,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -5759,7 +5790,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -5797,7 +5828,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -5835,7 +5866,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -5873,7 +5904,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -5911,7 +5942,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -5949,7 +5980,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -5987,7 +6018,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -6025,7 +6056,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -6063,7 +6094,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -6101,7 +6132,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -6139,7 +6170,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -6177,7 +6208,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -6215,7 +6246,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -6253,7 +6284,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -6291,7 +6322,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -6329,7 +6360,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -6367,7 +6398,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -6405,7 +6436,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -6443,7 +6474,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -6481,7 +6512,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -6519,7 +6550,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -6557,7 +6588,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -6595,7 +6626,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -6633,7 +6664,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -6671,7 +6702,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -6709,7 +6740,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -6747,7 +6778,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -6785,7 +6816,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -6823,7 +6854,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -6861,7 +6892,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -6899,7 +6930,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -6937,7 +6968,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -6975,7 +7006,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>114</v>
       </c>
@@ -7030,18 +7061,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
